--- a/artfynd/A 20741-2021 artfynd.xlsx
+++ b/artfynd/A 20741-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121502619</v>
+        <v>121502611</v>
       </c>
       <c r="B2" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639273</v>
+        <v>639309</v>
       </c>
       <c r="R2" t="n">
-        <v>6977871</v>
+        <v>6977752</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en granlåga. Skogen är gallrad</t>
+          <t>På en granlåga. Skogen gallrad.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121502611</v>
+        <v>121502619</v>
       </c>
       <c r="B3" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639309</v>
+        <v>639273</v>
       </c>
       <c r="R3" t="n">
-        <v>6977752</v>
+        <v>6977871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en granlåga. Skogen gallrad.</t>
+          <t>På en granlåga. Skogen är gallrad</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 20741-2021 artfynd.xlsx
+++ b/artfynd/A 20741-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121502611</v>
+        <v>121502619</v>
       </c>
       <c r="B2" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639309</v>
+        <v>639273</v>
       </c>
       <c r="R2" t="n">
-        <v>6977752</v>
+        <v>6977871</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en granlåga. Skogen gallrad.</t>
+          <t>På en granlåga. Skogen är gallrad</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121502619</v>
+        <v>121502611</v>
       </c>
       <c r="B3" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639273</v>
+        <v>639309</v>
       </c>
       <c r="R3" t="n">
-        <v>6977871</v>
+        <v>6977752</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en granlåga. Skogen är gallrad</t>
+          <t>På en granlåga. Skogen gallrad.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 20741-2021 artfynd.xlsx
+++ b/artfynd/A 20741-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121502619</v>
       </c>
       <c r="B2" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>121502611</v>
       </c>
       <c r="B3" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 20741-2021 artfynd.xlsx
+++ b/artfynd/A 20741-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121502611</v>
+        <v>121502619</v>
       </c>
       <c r="B2" t="n">
         <v>90693</v>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639309</v>
+        <v>639273</v>
       </c>
       <c r="R2" t="n">
-        <v>6977752</v>
+        <v>6977871</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en granlåga. Skogen gallrad.</t>
+          <t>På en granlåga. Skogen är gallrad</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121502619</v>
+        <v>121502611</v>
       </c>
       <c r="B3" t="n">
         <v>90693</v>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639273</v>
+        <v>639309</v>
       </c>
       <c r="R3" t="n">
-        <v>6977871</v>
+        <v>6977752</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en granlåga. Skogen är gallrad</t>
+          <t>På en granlåga. Skogen gallrad.</t>
         </is>
       </c>
       <c r="AD3" t="b">
